--- a/2022 data/excel_outputs/206_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/206_boothwise_data.xlsx
@@ -14,11 +14,80 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="446">
   <si>
     <t>AC 206 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -484,7 +553,7 @@
     <t>PRIMARY SCHOOL BALETHA HAMLET MANDAULEE ROOM NO. 2</t>
   </si>
   <si>
-    <t>■■■■■■■■ ■■■■■■■■ ■■■■■ ■■■■ ■■■■■■ PRIMARY SCHOOL GUESAR HAMLET MANDAULEE</t>
+    <t>PRIMARY SCHOOL PRATAPPUR NALA</t>
   </si>
   <si>
     <t>PRIMARY SCHOOL NIJAMATPUR</t>
@@ -542,9 +611,6 @@
   </si>
   <si>
     <t>JUNIYAR HIGH SCHOOL ARASHADPUR ROOM NO. 2</t>
-  </si>
-  <si>
-    <t>PRIMARY SCHOOL PRATAPPUR NALA</t>
   </si>
   <si>
     <t>PRIMARY SCHOOL KESHARINIVADA HAMLET HEERAMANSHIVLI</t>
@@ -1292,8 +1358,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1309,7 +1383,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1317,12 +1391,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1621,82 +1713,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="D2" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="E2" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="F2" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="G2" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="H2" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="I2" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="J2" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="K2" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="L2" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="M2" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="N2" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="O2" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="P2" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="Q2" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="R2" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="S2" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="T2" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="U2" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="V2" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="W2" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="X2" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1704,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>878</v>
@@ -1778,7 +1939,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>496</v>
@@ -1852,7 +2013,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>944</v>
@@ -1926,7 +2087,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>820</v>
@@ -2000,7 +2161,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>959</v>
@@ -2074,7 +2235,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>882</v>
@@ -2148,7 +2309,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>415</v>
@@ -2222,7 +2383,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>818</v>
@@ -2296,7 +2457,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>732</v>
@@ -2370,7 +2531,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>919</v>
@@ -2444,7 +2605,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>1066</v>
@@ -2518,7 +2679,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>998</v>
@@ -2592,7 +2753,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>764</v>
@@ -2666,7 +2827,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>911</v>
@@ -2740,7 +2901,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>938</v>
@@ -2814,7 +2975,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C18">
         <v>709</v>
@@ -2888,7 +3049,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <v>828</v>
@@ -2962,7 +3123,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C20">
         <v>632</v>
@@ -3036,7 +3197,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C21">
         <v>612</v>
@@ -3110,7 +3271,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <v>661</v>
@@ -3184,7 +3345,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>952</v>
@@ -3258,7 +3419,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>848</v>
@@ -3332,7 +3493,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>809</v>
@@ -3406,7 +3567,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C26">
         <v>1037</v>
@@ -3480,7 +3641,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>897</v>
@@ -3554,7 +3715,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>999</v>
@@ -3628,7 +3789,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>1010</v>
@@ -3702,7 +3863,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>1199</v>
@@ -3776,7 +3937,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>438</v>
@@ -3850,7 +4011,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C32">
         <v>707</v>
@@ -3924,7 +4085,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <v>715</v>
@@ -3998,7 +4159,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <v>485</v>
@@ -4072,7 +4233,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>922</v>
@@ -4146,7 +4307,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>1165</v>
@@ -4220,7 +4381,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>1111</v>
@@ -4294,7 +4455,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>1129</v>
@@ -4368,7 +4529,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>648</v>
@@ -4442,7 +4603,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>1058</v>
@@ -4516,7 +4677,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C41">
         <v>795</v>
@@ -4590,7 +4751,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>1039</v>
@@ -4664,7 +4825,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>1096</v>
@@ -4738,7 +4899,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>1005</v>
@@ -4812,7 +4973,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>1012</v>
@@ -4886,7 +5047,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>814</v>
@@ -4960,7 +5121,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>740</v>
@@ -5034,7 +5195,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>731</v>
@@ -5108,7 +5269,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>1051</v>
@@ -5182,7 +5343,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="C50">
         <v>1061</v>
@@ -5256,7 +5417,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>793</v>
@@ -5330,7 +5491,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C52">
         <v>361</v>
@@ -5404,7 +5565,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>608</v>
@@ -5478,7 +5639,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>440</v>
@@ -5552,7 +5713,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>1063</v>
@@ -5626,7 +5787,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>1187</v>
@@ -5700,7 +5861,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C57">
         <v>797</v>
@@ -5774,7 +5935,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C58">
         <v>1079</v>
@@ -5848,7 +6009,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C59">
         <v>956</v>
@@ -5922,7 +6083,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C60">
         <v>828</v>
@@ -5996,7 +6157,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>935</v>
@@ -6070,7 +6231,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C62">
         <v>909</v>
@@ -6144,7 +6305,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>957</v>
@@ -6218,7 +6379,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C64">
         <v>769</v>
@@ -6292,7 +6453,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C65">
         <v>637</v>
@@ -6366,7 +6527,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C66">
         <v>507</v>
@@ -6440,7 +6601,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>694</v>
@@ -6514,7 +6675,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>933</v>
@@ -6588,7 +6749,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C69">
         <v>619</v>
@@ -6662,7 +6823,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C70">
         <v>856</v>
@@ -6736,7 +6897,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>1123</v>
@@ -6810,7 +6971,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>883</v>
@@ -6884,7 +7045,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>1012</v>
@@ -6958,7 +7119,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>884</v>
@@ -7032,7 +7193,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C75">
         <v>1241</v>
@@ -7106,7 +7267,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>1041</v>
@@ -7180,7 +7341,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>731</v>
@@ -7254,7 +7415,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>812</v>
@@ -7328,7 +7489,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>700</v>
@@ -7402,7 +7563,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>838</v>
@@ -7476,7 +7637,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>1234</v>
@@ -7550,7 +7711,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>1154</v>
@@ -7624,7 +7785,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="C83">
         <v>1113</v>
@@ -7698,7 +7859,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>644</v>
@@ -7772,7 +7933,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="C85">
         <v>645</v>
@@ -7846,7 +8007,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C86">
         <v>239</v>
@@ -7920,7 +8081,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C87">
         <v>767</v>
@@ -7994,7 +8155,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C88">
         <v>1006</v>
@@ -8068,7 +8229,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C89">
         <v>1173</v>
@@ -8142,7 +8303,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C90">
         <v>877</v>
@@ -8216,7 +8377,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C91">
         <v>875</v>
@@ -8290,7 +8451,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C92">
         <v>720</v>
@@ -8364,7 +8525,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C93">
         <v>684</v>
@@ -8438,7 +8599,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C94">
         <v>694</v>
@@ -8512,7 +8673,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C95">
         <v>781</v>
@@ -8586,7 +8747,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C96">
         <v>1196</v>
@@ -8660,7 +8821,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C97">
         <v>685</v>
@@ -8734,7 +8895,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="C98">
         <v>1083</v>
@@ -8808,7 +8969,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C99">
         <v>569</v>
@@ -8882,7 +9043,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>589</v>
@@ -8956,7 +9117,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C101">
         <v>585</v>
@@ -9030,7 +9191,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="C102">
         <v>449</v>
@@ -9104,7 +9265,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C103">
         <v>800</v>
@@ -9178,7 +9339,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C104">
         <v>704</v>
@@ -9252,7 +9413,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C105">
         <v>478</v>
@@ -9326,7 +9487,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C106">
         <v>527</v>
@@ -9400,7 +9561,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C107">
         <v>688</v>
@@ -9474,7 +9635,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="C108">
         <v>823</v>
@@ -9548,7 +9709,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="C109">
         <v>402</v>
@@ -9622,7 +9783,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C110">
         <v>825</v>
@@ -9696,7 +9857,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C111">
         <v>624</v>
@@ -9770,7 +9931,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="C112">
         <v>604</v>
@@ -9844,7 +10005,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C113">
         <v>466</v>
@@ -9918,7 +10079,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="C114">
         <v>808</v>
@@ -9992,7 +10153,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C115">
         <v>527</v>
@@ -10066,7 +10227,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="C116">
         <v>935</v>
@@ -10140,7 +10301,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C117">
         <v>491</v>
@@ -10214,7 +10375,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C118">
         <v>319</v>
@@ -10288,7 +10449,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C119">
         <v>811</v>
@@ -10362,7 +10523,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C120">
         <v>453</v>
@@ -10436,7 +10597,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C121">
         <v>1220</v>
@@ -10510,7 +10671,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="C122">
         <v>457</v>
@@ -10584,7 +10745,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>551</v>
@@ -10658,7 +10819,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C124">
         <v>691</v>
@@ -10732,7 +10893,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C125">
         <v>660</v>
@@ -10806,7 +10967,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C126">
         <v>623</v>
@@ -10880,7 +11041,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C127">
         <v>624</v>
@@ -10954,7 +11115,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C128">
         <v>910</v>
@@ -11028,7 +11189,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="C129">
         <v>569</v>
@@ -11102,7 +11263,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C130">
         <v>944</v>
@@ -11176,7 +11337,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="C131">
         <v>1186</v>
@@ -11250,7 +11411,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C132">
         <v>347</v>
@@ -11324,7 +11485,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="C133">
         <v>1048</v>
@@ -11398,7 +11559,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="C134">
         <v>1009</v>
@@ -11472,7 +11633,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C135">
         <v>543</v>
@@ -11546,7 +11707,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C136">
         <v>610</v>
@@ -11620,7 +11781,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C137">
         <v>608</v>
@@ -11694,7 +11855,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="C138">
         <v>800</v>
@@ -11768,7 +11929,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="C139">
         <v>748</v>
@@ -11842,7 +12003,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C140">
         <v>1056</v>
@@ -11916,7 +12077,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="C141">
         <v>949</v>
@@ -11990,7 +12151,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C142">
         <v>976</v>
@@ -12064,7 +12225,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C143">
         <v>681</v>
@@ -12138,7 +12299,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="C144">
         <v>693</v>
@@ -12212,7 +12373,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C145">
         <v>479</v>
@@ -12286,7 +12447,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C146">
         <v>956</v>
@@ -12360,7 +12521,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="C147">
         <v>1101</v>
@@ -12434,7 +12595,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C148">
         <v>843</v>
@@ -12508,7 +12669,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="C149">
         <v>1100</v>
@@ -12582,7 +12743,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="C150">
         <v>1077</v>
@@ -12656,7 +12817,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="C151">
         <v>600</v>
@@ -12730,7 +12891,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C152">
         <v>404</v>
@@ -12804,7 +12965,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="C153">
         <v>268</v>
@@ -12878,7 +13039,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C154">
         <v>1025</v>
@@ -12952,7 +13113,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="C155">
         <v>769</v>
@@ -13026,7 +13187,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C156">
         <v>250</v>
@@ -13100,7 +13261,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C157">
         <v>725</v>
@@ -13174,7 +13335,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C158">
         <v>345</v>
@@ -13248,7 +13409,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C159">
         <v>732</v>
@@ -13322,7 +13483,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="C160">
         <v>978</v>
@@ -13396,7 +13557,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C161">
         <v>605</v>
@@ -13470,7 +13631,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C162">
         <v>665</v>
@@ -13544,7 +13705,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="C163">
         <v>821</v>
@@ -13618,7 +13779,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="C164">
         <v>600</v>
@@ -13692,7 +13853,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C165">
         <v>747</v>
@@ -13766,7 +13927,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="C166">
         <v>988</v>
@@ -13840,7 +14001,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C167">
         <v>530</v>
@@ -13914,7 +14075,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="C168">
         <v>430</v>
@@ -13988,7 +14149,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="C169">
         <v>783</v>
@@ -14062,7 +14223,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C170">
         <v>576</v>
@@ -14136,7 +14297,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="C171">
         <v>936</v>
@@ -14210,7 +14371,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C172">
         <v>640</v>
@@ -14284,7 +14445,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="C173">
         <v>668</v>
@@ -14358,7 +14519,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C174">
         <v>1104</v>
@@ -14432,7 +14593,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="C175">
         <v>664</v>
@@ -14506,7 +14667,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C176">
         <v>319</v>
@@ -14580,7 +14741,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="C177">
         <v>859</v>
@@ -14654,7 +14815,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="C178">
         <v>437</v>
@@ -14728,7 +14889,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C179">
         <v>1011</v>
@@ -14802,7 +14963,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="C180">
         <v>743</v>
@@ -14876,7 +15037,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C181">
         <v>1189</v>
@@ -14950,7 +15111,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C182">
         <v>1020</v>
@@ -15024,7 +15185,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="C183">
         <v>495</v>
@@ -15098,7 +15259,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C184">
         <v>545</v>
@@ -15172,7 +15333,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="C185">
         <v>529</v>
@@ -15246,7 +15407,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="C186">
         <v>856</v>
@@ -15320,7 +15481,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C187">
         <v>707</v>
@@ -15394,7 +15555,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="C188">
         <v>683</v>
@@ -15468,7 +15629,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C189">
         <v>676</v>
@@ -15542,7 +15703,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="C190">
         <v>525</v>
@@ -15616,7 +15777,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>667</v>
@@ -15690,7 +15851,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C192">
         <v>814</v>
@@ -15764,7 +15925,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="C193">
         <v>655</v>
@@ -15838,7 +15999,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="C194">
         <v>691</v>
@@ -15912,7 +16073,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C195">
         <v>631</v>
@@ -15986,7 +16147,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C196">
         <v>624</v>
@@ -16060,7 +16221,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C197">
         <v>322</v>
@@ -16134,7 +16295,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C198">
         <v>1000</v>
@@ -16208,7 +16369,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C199">
         <v>535</v>
@@ -16282,7 +16443,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="C200">
         <v>845</v>
@@ -16356,7 +16517,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="C201">
         <v>743</v>
@@ -16430,7 +16591,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="C202">
         <v>885</v>
@@ -16504,7 +16665,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="C203">
         <v>991</v>
@@ -16578,7 +16739,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="C204">
         <v>925</v>
@@ -16652,7 +16813,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C205">
         <v>832</v>
@@ -16726,7 +16887,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="C206">
         <v>1158</v>
@@ -16800,7 +16961,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="C207">
         <v>697</v>
@@ -16874,7 +17035,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="C208">
         <v>838</v>
@@ -16948,7 +17109,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="C209">
         <v>1080</v>
@@ -17022,7 +17183,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="C210">
         <v>623</v>
@@ -17096,7 +17257,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="C211">
         <v>440</v>
@@ -17170,7 +17331,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C212">
         <v>427</v>
@@ -17244,7 +17405,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="C213">
         <v>698</v>
@@ -17318,7 +17479,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="C214">
         <v>579</v>
@@ -17392,7 +17553,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C215">
         <v>1123</v>
@@ -17466,7 +17627,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="C216">
         <v>1091</v>
@@ -17540,7 +17701,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="C217">
         <v>1107</v>
@@ -17614,7 +17775,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C218">
         <v>548</v>
@@ -17688,7 +17849,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="C219">
         <v>659</v>
@@ -17762,7 +17923,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C220">
         <v>663</v>
@@ -17836,7 +17997,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="C221">
         <v>1169</v>
@@ -17910,7 +18071,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="C222">
         <v>871</v>
@@ -17984,7 +18145,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="C223">
         <v>667</v>
@@ -18058,7 +18219,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="C224">
         <v>666</v>
@@ -18132,7 +18293,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="C225">
         <v>687</v>
@@ -18206,7 +18367,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C226">
         <v>1186</v>
@@ -18280,7 +18441,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="C227">
         <v>567</v>
@@ -18354,7 +18515,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="C228">
         <v>696</v>
@@ -18428,7 +18589,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C229">
         <v>716</v>
@@ -18502,7 +18663,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="C230">
         <v>645</v>
@@ -18576,7 +18737,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="C231">
         <v>774</v>
@@ -18650,7 +18811,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="C232">
         <v>628</v>
@@ -18724,7 +18885,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="C233">
         <v>410</v>
@@ -18798,7 +18959,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="C234">
         <v>851</v>
@@ -18872,7 +19033,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C235">
         <v>1047</v>
@@ -18946,7 +19107,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="C236">
         <v>897</v>
@@ -19020,7 +19181,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="C237">
         <v>559</v>
@@ -19094,7 +19255,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C238">
         <v>535</v>
@@ -19168,7 +19329,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="C239">
         <v>900</v>
@@ -19242,7 +19403,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="C240">
         <v>465</v>
@@ -19316,7 +19477,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C241">
         <v>672</v>
@@ -19390,7 +19551,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="C242">
         <v>663</v>
@@ -19464,7 +19625,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C243">
         <v>674</v>
@@ -19538,7 +19699,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C244">
         <v>623</v>
@@ -19612,7 +19773,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="C245">
         <v>763</v>
@@ -19686,7 +19847,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C246">
         <v>513</v>
@@ -19760,7 +19921,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C247">
         <v>638</v>
@@ -19834,7 +19995,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C248">
         <v>771</v>
@@ -19908,7 +20069,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="C249">
         <v>692</v>
@@ -19982,7 +20143,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C250">
         <v>791</v>
@@ -20056,7 +20217,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="C251">
         <v>775</v>
@@ -20130,7 +20291,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="C252">
         <v>836</v>
@@ -20204,7 +20365,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C253">
         <v>641</v>
@@ -20278,7 +20439,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="C254">
         <v>593</v>
@@ -20352,7 +20513,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C255">
         <v>1011</v>
@@ -20426,7 +20587,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C256">
         <v>850</v>
@@ -20500,7 +20661,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C257">
         <v>660</v>
@@ -20574,7 +20735,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="C258">
         <v>256</v>
@@ -20648,7 +20809,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C259">
         <v>1112</v>
@@ -20722,7 +20883,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C260">
         <v>1118</v>
@@ -20796,7 +20957,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="C261">
         <v>668</v>
@@ -20870,7 +21031,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C262">
         <v>921</v>
@@ -20944,7 +21105,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C263">
         <v>645</v>
@@ -21018,7 +21179,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="C264">
         <v>1019</v>
@@ -21092,7 +21253,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C265">
         <v>1089</v>
@@ -21166,7 +21327,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C266">
         <v>1061</v>
@@ -21240,7 +21401,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="C267">
         <v>1222</v>
@@ -21314,7 +21475,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C268">
         <v>868</v>
@@ -21388,7 +21549,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="C269">
         <v>992</v>
@@ -21462,7 +21623,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="C270">
         <v>831</v>
@@ -21536,7 +21697,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="C271">
         <v>1010</v>
@@ -21610,7 +21771,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C272">
         <v>1179</v>
@@ -21684,7 +21845,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="C273">
         <v>691</v>
@@ -21758,7 +21919,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="C274">
         <v>701</v>
@@ -21832,7 +21993,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="C275">
         <v>1064</v>
@@ -21906,7 +22067,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="C276">
         <v>1082</v>
@@ -21980,7 +22141,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="C277">
         <v>1117</v>
@@ -22054,7 +22215,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C278">
         <v>804</v>
@@ -22128,7 +22289,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="C279">
         <v>1148</v>
@@ -22202,7 +22363,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="C280">
         <v>657</v>
@@ -22276,7 +22437,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C281">
         <v>691</v>
@@ -22350,7 +22511,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="C282">
         <v>688</v>
@@ -22424,7 +22585,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C283">
         <v>742</v>
@@ -22498,7 +22659,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="C284">
         <v>904</v>
@@ -22572,7 +22733,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="C285">
         <v>502</v>
@@ -22646,7 +22807,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C286">
         <v>703</v>
@@ -22720,7 +22881,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="C287">
         <v>801</v>
@@ -22794,7 +22955,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="C288">
         <v>1110</v>
@@ -22868,7 +23029,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C289">
         <v>930</v>
@@ -22942,7 +23103,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="C290">
         <v>1169</v>
@@ -23016,7 +23177,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="C291">
         <v>998</v>
@@ -23090,7 +23251,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="C292">
         <v>888</v>
@@ -23164,7 +23325,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="C293">
         <v>624</v>
@@ -23238,7 +23399,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="C294">
         <v>458</v>
@@ -23312,7 +23473,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="C295">
         <v>1113</v>
@@ -23386,7 +23547,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="C296">
         <v>633</v>
@@ -23460,7 +23621,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="C297">
         <v>729</v>
@@ -23534,7 +23695,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="C298">
         <v>803</v>
@@ -23608,7 +23769,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="C299">
         <v>1012</v>
@@ -23682,7 +23843,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="C300">
         <v>860</v>
@@ -23756,7 +23917,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="C301">
         <v>1121</v>
@@ -23830,7 +23991,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="C302">
         <v>975</v>
@@ -23904,7 +24065,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C303">
         <v>1087</v>
@@ -23978,7 +24139,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C304">
         <v>422</v>
@@ -24052,7 +24213,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="C305">
         <v>1046</v>
@@ -24126,7 +24287,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="C306">
         <v>951</v>
@@ -24200,7 +24361,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="C307">
         <v>671</v>
@@ -24274,7 +24435,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="C308">
         <v>1103</v>
@@ -24348,7 +24509,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="C309">
         <v>837</v>
@@ -24422,7 +24583,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="C310">
         <v>721</v>
@@ -24496,7 +24657,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="C311">
         <v>645</v>
@@ -24570,7 +24731,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="C312">
         <v>860</v>
@@ -24644,7 +24805,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="C313">
         <v>556</v>
@@ -24718,7 +24879,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="C314">
         <v>1096</v>
@@ -24792,7 +24953,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="C315">
         <v>927</v>
@@ -24866,7 +25027,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="C316">
         <v>1076</v>
@@ -24940,7 +25101,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="C317">
         <v>946</v>
@@ -25014,7 +25175,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="C318">
         <v>817</v>
@@ -25088,7 +25249,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="C319">
         <v>1002</v>
@@ -25162,7 +25323,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="C320">
         <v>485</v>
@@ -25236,7 +25397,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="C321">
         <v>1195</v>
@@ -25310,7 +25471,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C322">
         <v>617</v>
@@ -25384,7 +25545,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="C323">
         <v>765</v>
@@ -25458,7 +25619,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="C324">
         <v>955</v>
@@ -25532,7 +25693,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C325">
         <v>967</v>
@@ -25606,7 +25767,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="C326">
         <v>632</v>
@@ -25680,7 +25841,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="C327">
         <v>807</v>
@@ -25754,7 +25915,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C328">
         <v>538</v>
@@ -25828,7 +25989,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C329">
         <v>1118</v>
@@ -25902,7 +26063,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="C330">
         <v>1118</v>
@@ -25976,7 +26137,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="C331">
         <v>666</v>
@@ -26050,7 +26211,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="C332">
         <v>1236</v>
@@ -26124,7 +26285,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="C333">
         <v>975</v>
@@ -26198,7 +26359,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="C334">
         <v>433</v>
@@ -26272,7 +26433,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="C335">
         <v>771</v>
@@ -26346,7 +26507,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="C336">
         <v>729</v>
@@ -26420,7 +26581,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C337">
         <v>919</v>
@@ -26494,7 +26655,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="C338">
         <v>903</v>
@@ -26568,7 +26729,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="C339">
         <v>816</v>
@@ -26642,7 +26803,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="C340">
         <v>769</v>
@@ -26716,7 +26877,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="C341">
         <v>1082</v>
@@ -26790,7 +26951,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="C342">
         <v>1038</v>
@@ -26864,7 +27025,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="C343">
         <v>1005</v>
@@ -26938,7 +27099,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="C344">
         <v>837</v>
@@ -27012,7 +27173,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="C345">
         <v>768</v>
@@ -27086,7 +27247,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="C346">
         <v>528</v>
@@ -27160,7 +27321,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="C347">
         <v>752</v>
@@ -27234,7 +27395,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="C348">
         <v>960</v>
@@ -27308,7 +27469,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="C349">
         <v>968</v>
@@ -27382,7 +27543,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C350">
         <v>1174</v>
@@ -27456,7 +27617,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="C351">
         <v>908</v>
@@ -27530,7 +27691,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="C352">
         <v>888</v>
@@ -27604,7 +27765,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="C353">
         <v>920</v>
@@ -27678,7 +27839,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="C354">
         <v>969</v>
@@ -27752,7 +27913,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="C355">
         <v>1195</v>
@@ -27826,7 +27987,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="C356">
         <v>922</v>
@@ -27900,7 +28061,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="C357">
         <v>887</v>
@@ -27974,7 +28135,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="C358">
         <v>462</v>
@@ -28048,7 +28209,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="C359">
         <v>1073</v>
@@ -28122,7 +28283,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="C360">
         <v>1003</v>
@@ -28196,7 +28357,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="C361">
         <v>727</v>
@@ -28270,7 +28431,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="C362">
         <v>607</v>
@@ -28344,7 +28505,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C363">
         <v>1098</v>
@@ -28418,7 +28579,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="C364">
         <v>939</v>
@@ -28492,7 +28653,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="C365">
         <v>981</v>
@@ -28566,7 +28727,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="C366">
         <v>1112</v>
@@ -28640,7 +28801,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="C367">
         <v>1158</v>
@@ -28714,7 +28875,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="C368">
         <v>1149</v>
@@ -28788,7 +28949,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="C369">
         <v>945</v>
@@ -28862,7 +29023,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="C370">
         <v>1119</v>
@@ -28936,7 +29097,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="C371">
         <v>926</v>
@@ -29010,7 +29171,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="C372">
         <v>925</v>
@@ -29084,7 +29245,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="C373">
         <v>746</v>
@@ -29158,7 +29319,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="C374">
         <v>986</v>
@@ -29232,7 +29393,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="C375">
         <v>748</v>
@@ -29306,7 +29467,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="C376">
         <v>855</v>
@@ -29380,7 +29541,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="C377">
         <v>464</v>
@@ -29454,7 +29615,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="C378">
         <v>674</v>
@@ -29528,7 +29689,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="C379">
         <v>719</v>
@@ -29602,7 +29763,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="C380">
         <v>1084</v>
@@ -29676,7 +29837,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="C381">
         <v>950</v>
@@ -29750,7 +29911,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="C382">
         <v>1044</v>
@@ -29824,7 +29985,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="C383">
         <v>1004</v>
@@ -29898,7 +30059,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="C384">
         <v>1185</v>
@@ -29972,7 +30133,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="C385">
         <v>1139</v>
@@ -30046,7 +30207,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="C386">
         <v>618</v>
@@ -30120,7 +30281,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="C387">
         <v>686</v>
@@ -30194,7 +30355,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="C388">
         <v>813</v>
@@ -30268,7 +30429,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="C389">
         <v>633</v>
@@ -30342,7 +30503,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="C390">
         <v>1066</v>
@@ -30416,7 +30577,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="C391">
         <v>701</v>
@@ -30490,7 +30651,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C392">
         <v>743</v>
@@ -30564,7 +30725,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C393">
         <v>1032</v>
@@ -30638,7 +30799,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="C394">
         <v>944</v>
@@ -30712,7 +30873,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="C395">
         <v>897</v>
@@ -30786,7 +30947,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="C396">
         <v>823</v>
@@ -30860,7 +31021,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="C397">
         <v>1208</v>
@@ -30934,7 +31095,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="C398">
         <v>865</v>
@@ -31008,7 +31169,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="C399">
         <v>945</v>
@@ -31082,7 +31243,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="C400">
         <v>841</v>
@@ -31156,7 +31317,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="C401">
         <v>711</v>
@@ -31230,7 +31391,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="C402">
         <v>1036</v>
@@ -31304,7 +31465,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="C403">
         <v>696</v>
